--- a/filer/19555305_bauhaus.xlsx
+++ b/filer/19555305_bauhaus.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/19555305_bauhaus.xlsx
+++ b/filer/19555305_bauhaus.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_19555305" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_19555305" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_19555305" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_19555305" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,9 +193,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +630,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +645,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1499,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2688,35 +2689,35 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
@@ -4070,19 +4071,19 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
@@ -4188,19 +4189,19 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
@@ -4497,6 +4498,148 @@
       </c>
       <c r="F93" s="13">
         <f>IFERROR($F$30/($F$55+$F$62)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw_19555305'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw_19555305'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw_19555305'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw_19555305'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw_19555305'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_19555305'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_19555305'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_19555305'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_19555305'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_19555305'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_19555305'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_19555305'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_19555305'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_19555305'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_19555305'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_19555305'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_19555305'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_19555305'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_19555305'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_19555305'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B100">
+        <f>IF(ABS(('pengestrom_raw_19555305'!$B$2+'pengestrom_raw_19555305'!$B$3+'pengestrom_raw_19555305'!$B$4)-'pengestrom_raw_19555305'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19555305'!$B$2+'pengestrom_raw_19555305'!$B$3+'pengestrom_raw_19555305'!$B$4)-'pengestrom_raw_19555305'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C100">
+        <f>IF(ABS(('pengestrom_raw_19555305'!$C$2+'pengestrom_raw_19555305'!$C$3+'pengestrom_raw_19555305'!$C$4)-'pengestrom_raw_19555305'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19555305'!$C$2+'pengestrom_raw_19555305'!$C$3+'pengestrom_raw_19555305'!$C$4)-'pengestrom_raw_19555305'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D100">
+        <f>IF(ABS(('pengestrom_raw_19555305'!$D$2+'pengestrom_raw_19555305'!$D$3+'pengestrom_raw_19555305'!$D$4)-'pengestrom_raw_19555305'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19555305'!$D$2+'pengestrom_raw_19555305'!$D$3+'pengestrom_raw_19555305'!$D$4)-'pengestrom_raw_19555305'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E100">
+        <f>IF(ABS(('pengestrom_raw_19555305'!$E$2+'pengestrom_raw_19555305'!$E$3+'pengestrom_raw_19555305'!$E$4)-'pengestrom_raw_19555305'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19555305'!$E$2+'pengestrom_raw_19555305'!$E$3+'pengestrom_raw_19555305'!$E$4)-'pengestrom_raw_19555305'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F100">
+        <f>IF(ABS(('pengestrom_raw_19555305'!$F$2+'pengestrom_raw_19555305'!$F$3+'pengestrom_raw_19555305'!$F$4)-'pengestrom_raw_19555305'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19555305'!$F$2+'pengestrom_raw_19555305'!$F$3+'pengestrom_raw_19555305'!$F$4)-'pengestrom_raw_19555305'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4529,379 +4672,381 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>3195673</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>3066793</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>3003311</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>2796892</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>2844360</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>2959613</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>4814</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>3503</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>4846</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>4105</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>2819</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>2847</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>1935106</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>1869021</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>1886147</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>1778980</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>1804016</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>1814362</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>455099</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>470806</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>479214</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>479086</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>500025</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>505728</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>810282</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>730469</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>642796</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>542931</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>543138</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>642370</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>455587</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>440132</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>451591</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>435193</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>439563</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>463171</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>60561</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>65506</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>68741</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>76967</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>68385</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>59134</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n">
         <v>2664</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>465</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>787</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>708</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>294134</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>224831</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>119800</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>30306</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>34403</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>119357</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>328</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>3229</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>6085</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>5993</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>287366</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>220032</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>116623</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>31717</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>38892</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>124233</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>63740</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>48492</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>25969</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>6995</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>8704</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>27451</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>223626</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>171540</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>90654</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>24722</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>30188</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>96782</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>1129</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>1113</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>1134</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>1095</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>1001</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>1003</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4932,967 +5077,963 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>18141</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>22007</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>42220</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>23305</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>8649</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>9541</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>185487</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>189059</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>217810</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>211478</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>204868</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>194529</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>16680</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>14260</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>11178</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>19221</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>17615</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>16838</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>202167</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>203319</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>228988</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>230699</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>222483</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>211367</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>220308</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>225326</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>271208</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>254004</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>231132</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>220908</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>658383</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>672250</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>793657</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>769481</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>722739</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>791746</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>658383</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>672250</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>793657</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>769481</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>722739</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>791746</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>38198</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>57797</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>37192</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>83608</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>74415</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>47743</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>10501</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>47314</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>65559</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>32939</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>3195</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>29943</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>808</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>14365</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>4254</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>6725</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>7203</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>5032</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>8775</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>435</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>6336</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>9642</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>42348</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>32288</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>64042</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>62603</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>25631</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>18211</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>98262</v>
-      </c>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>142551</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>176376</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>193950</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>113831</v>
       </c>
+      <c r="F21" s="17" t="n">
+        <v>112264</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>37672</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>127204</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>60423</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>77537</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>216020</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>288703</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>794317</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>942005</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>1030456</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>1040968</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>1052590</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>1192713</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>1014625</v>
-      </c>
-      <c r="C25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>1167331</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>1301664</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>1294972</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>1283722</v>
       </c>
+      <c r="F25" s="17" t="n">
+        <v>1413621</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>32000</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>32000</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>32000</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>32000</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>32000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>548148</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>719688</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>810342</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>835064</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>865252</v>
       </c>
+      <c r="F31" s="17" t="n">
+        <v>962034</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
-        <v>580148</v>
-      </c>
-      <c r="C32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>751688</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>842342</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>867064</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>897252</v>
       </c>
+      <c r="F32" s="17" t="n">
+        <v>994034</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
-        <v>8183</v>
-      </c>
-      <c r="C33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>9926</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>16993</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>13055</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>10128</v>
       </c>
+      <c r="F33" s="17" t="n">
+        <v>8707</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>8183</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>9926</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>16993</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>13055</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>10128</v>
       </c>
+      <c r="F34" s="17" t="n">
+        <v>8707</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>4887</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>3576</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>3298</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>3443</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>4221</v>
       </c>
+      <c r="F37" s="17" t="n">
+        <v>6100</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>100000</v>
       </c>
-      <c r="C38" s="16" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>135244</v>
-      </c>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>103576</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>3298</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>3443</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>4221</v>
       </c>
+      <c r="F39" s="17" t="n">
+        <v>6100</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
-        <v>2963</v>
-      </c>
-      <c r="C41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>2769</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>3068</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>4881</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="E41" s="17" t="n">
         <v>3723</v>
       </c>
+      <c r="F41" s="17" t="n">
+        <v>3677</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
-        <v>24848</v>
-      </c>
-      <c r="C42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>2903</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>1443</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="16" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>149898</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>163970</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>179229</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>257164</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="E44" s="17" t="n">
         <v>245732</v>
       </c>
+      <c r="F44" s="17" t="n">
+        <v>273688</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>12700</v>
-      </c>
-      <c r="C45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>3584</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>139336</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>17821</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>7807</v>
       </c>
+      <c r="F45" s="17" t="n">
+        <v>9867</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
-        <v>98197</v>
-      </c>
-      <c r="C49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>125298</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>111577</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>129594</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>112173</v>
       </c>
+      <c r="F49" s="17" t="n">
+        <v>116338</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
-        <v>2444</v>
-      </c>
-      <c r="C50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>3617</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>4378</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>1950</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>2686</v>
       </c>
+      <c r="F50" s="17" t="n">
+        <v>1210</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
-        <v>291050</v>
-      </c>
-      <c r="C51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>302141</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>439031</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>411410</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>372121</v>
       </c>
+      <c r="F51" s="17" t="n">
+        <v>404780</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>426294</v>
-      </c>
-      <c r="C52" s="16" t="n">
+      <c r="B52" s="17" t="n">
         <v>405717</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>442329</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>414853</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="E52" s="17" t="n">
         <v>376342</v>
       </c>
+      <c r="F52" s="17" t="n">
+        <v>410880</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>1014625</v>
-      </c>
-      <c r="C53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>1167331</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>1301664</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>1294972</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>1283722</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>1413621</v>
       </c>
     </row>
   </sheetData>
@@ -5901,6 +6042,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>184758</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>156672</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>74039</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>184376</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>118646</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-72168</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-119465</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-59535</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-45468</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-47796</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-102528</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>4053</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-425</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5931,13 +6194,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6651,7 +6914,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6769,7 +7032,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6945,7 +7208,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
